--- a/r5-TC-FHIR-AG-Scheduling-R5-133-56---resolve-todo-for-example-search-urls/all-profiles.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-133-56---resolve-todo-for-example-search-urls/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/appointment-booking-url</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/appointment-booking-url</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:33:33+00:00</t>
+    <t>2026-08-18T09:10:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -336,7 +336,7 @@
     <t>appointment-postponementReason</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/appointment-postponementReason</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/appointment-postponementReason</t>
   </si>
   <si>
     <t>AppointmentPostponementReasonExt</t>
@@ -364,7 +364,7 @@
     <t>at-scheduling-appointment</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-appointment</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-appointment</t>
   </si>
   <si>
     <t>HL7ATSchedulingAppointment</t>
@@ -538,7 +538,7 @@
     <t>postponementReason</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/appointment-postponementReason}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/appointment-postponementReason}
 </t>
   </si>
   <si>
@@ -638,7 +638,7 @@
     <t>cancellationPolicy</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-ext-cancellationPolicy}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-ext-cancellationPolicy}
 </t>
   </si>
   <si>
@@ -719,7 +719,7 @@
     <t>Appointment.serviceType</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableReference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice)
+    <t xml:space="preserve">CodeableReference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-healthcareservice)
 </t>
   </si>
   <si>
@@ -732,7 +732,7 @@
     <t>For a provider to provider appointment the code "FOLLOWUP" may be appropriate, as this is expected to be discussing some patient that was seen in the past.</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/ValueSet/AtSchedulingServiceType</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/ValueSet/AtSchedulingServiceType</t>
   </si>
   <si>
     <t>Appointment.specialty</t>
@@ -816,7 +816,7 @@
     <t>Appointment.replaces</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-appointment)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-appointment)
 </t>
   </si>
   <si>
@@ -954,7 +954,7 @@
     <t>Appointment.slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-slot)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-slot)
 </t>
   </si>
   <si>
@@ -1108,7 +1108,7 @@
     <t>virtualService</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/virtual-service-detail}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/virtual-service-detail}
 </t>
   </si>
   <si>
@@ -1828,7 +1828,7 @@
     <t>at-scheduling-ext-cancellationPolicy</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-ext-cancellationPolicy</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-ext-cancellationPolicy</t>
   </si>
   <si>
     <t>CancellationPolicy</t>
@@ -1909,7 +1909,7 @@
     <t>at-scheduling-healthcareservice</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-healthcareservice</t>
   </si>
   <si>
     <t>HL7® AT Scheduling HealthcareService Profile</t>
@@ -2004,7 +2004,7 @@
     <t>HealthcareService.offeredIn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-healthcareservice)
 </t>
   </si>
   <si>
@@ -2317,7 +2317,7 @@
     <t>at-scheduling-schedule</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-schedule</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-schedule</t>
   </si>
   <si>
     <t>HL7ATSchedulingSchedule</t>
@@ -2423,7 +2423,7 @@
     <t>Schedule.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-patient|http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-practitionerRole|CareTeam|RelatedPerson|Device|http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice|Location)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-patient|http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-practitionerRole|CareTeam|RelatedPerson|Device|https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-healthcareservice|Location)
 </t>
   </si>
   <si>
@@ -2457,7 +2457,7 @@
     <t>at-scheduling-slot</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-slot</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-slot</t>
   </si>
   <si>
     <t>HL7ATSchedulingSlot</t>
@@ -2508,7 +2508,7 @@
     <t>SlotEncounterClass</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/slot-encounter-class}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/slot-encounter-class}
 </t>
   </si>
   <si>
@@ -2524,7 +2524,7 @@
     <t>bookingURL</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/appointment-booking-url}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/appointment-booking-url}
 </t>
   </si>
   <si>
@@ -2567,7 +2567,7 @@
     <t>Slot.schedule</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-schedule)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-schedule)
 </t>
   </si>
   <si>
@@ -2634,7 +2634,7 @@
     <t>slot-encounter-class</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/slot-encounter-class</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/slot-encounter-class</t>
   </si>
   <si>
     <t>SlotEncounterClassExt</t>
@@ -2643,7 +2643,7 @@
     <t>virtual-service-detail</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/virtual-service-detail</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/virtual-service-detail</t>
   </si>
   <si>
     <t>VirtualServiceDetailExt</t>
@@ -4453,7 +4453,7 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="74.7578125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="65.6953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="58.328125" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>
